--- a/artfynd/A 52129-2023 artfynd.xlsx
+++ b/artfynd/A 52129-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52129-2023 artfynd.xlsx
+++ b/artfynd/A 52129-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>56219981</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519344.58659854</v>
+        <v>519345</v>
       </c>
       <c r="R2" t="n">
-        <v>7020592.346767919</v>
+        <v>7020592</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-10-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>56219982</v>
       </c>
       <c r="B3" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519351.8481585572</v>
+        <v>519352</v>
       </c>
       <c r="R3" t="n">
-        <v>7020582.500810594</v>
+        <v>7020583</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2014-10-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-10-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +874,309 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125228193</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långselfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>519377</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7020706</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125228201</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långselfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>519434</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7020735</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125228208</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långselfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>519464</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7020742</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Söderhjelm</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52129-2023 artfynd.xlsx
+++ b/artfynd/A 52129-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56219981</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56219982</t>
         </is>
       </c>
     </row>
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125228193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125228201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125228208</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>